--- a/InputData/io-model/PoNDHbE/Perc of National Debt Held by Entity.xlsx
+++ b/InputData/io-model/PoNDHbE/Perc of National Debt Held by Entity.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23801"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jeff-nonadmin\CodeRepositories\eps-us\InputData\io-model\PoNDHbE\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CodeRepositories\eps-us\InputData\io-model\PoNDHbE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65C0E6E5-8CEA-47EB-9224-2FF957AD31C3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9920A425-351B-4BCC-BB21-C89452DDEA92}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3450" yWindow="435" windowWidth="23955" windowHeight="16500" xr2:uid="{451D0B24-AF55-4E31-8A85-DA035DBAD1DC}"/>
+    <workbookView xWindow="9150" yWindow="690" windowWidth="29520" windowHeight="21060" xr2:uid="{451D0B24-AF55-4E31-8A85-DA035DBAD1DC}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="60">
   <si>
     <t>PoNDHbE Percent of National Debt Held by Entity</t>
   </si>
@@ -288,21 +288,6 @@
   </si>
   <si>
     <t>foreign entities</t>
-  </si>
-  <si>
-    <t>other energy suppliers</t>
-  </si>
-  <si>
-    <t>electricity suppliers</t>
-  </si>
-  <si>
-    <t>coal suppliers</t>
-  </si>
-  <si>
-    <t>natural gas and petroleum suppliers</t>
-  </si>
-  <si>
-    <t>biomass and biofuel suppliers</t>
   </si>
   <si>
     <t>Average % of Debt Held</t>
@@ -355,6 +340,9 @@
       </rPr>
       <t>exclude all intra-governmental debt</t>
     </r>
+  </si>
+  <si>
+    <t>domestic industry</t>
   </si>
 </sst>
 </file>
@@ -1069,47 +1057,47 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -3105,10 +3093,10 @@
         <v>42</v>
       </c>
       <c r="C1" s="30" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="D1" s="30" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -3263,7 +3251,7 @@
   <sheetPr>
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.85546875" customWidth="1"/>
@@ -3272,10 +3260,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="33" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B1" s="32" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -3288,7 +3276,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="B3">
         <f>SUM(Calcs!D3:D5,Calcs!D9)</f>
@@ -3311,46 +3299,6 @@
       <c r="B5">
         <f>Calcs!D8</f>
         <v>0.46119785168008015</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>47</v>
-      </c>
-      <c r="B6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>48</v>
-      </c>
-      <c r="B7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>49</v>
-      </c>
-      <c r="B8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>50</v>
-      </c>
-      <c r="B9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>46</v>
-      </c>
-      <c r="B10">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
